--- a/pensum/ok04/OK04_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok04/OK04_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="130">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 4: Regnskapsanalyse (V5)</t>
   </si>
@@ -143,18 +143,48 @@
     <t xml:space="preserve">a)  Totalkapitalrentabiliteten i prosent med én desimal: (resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TKR = (ordinært resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital (Økonomistyring 4.2.1). Gjennomsnitt = (IB + UB) / 2.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Gjennomsnittlig gjeldsrente i prosent med én desimal: rentekostnader × 100 / gjennomsnittlig gjeld.</t>
   </si>
   <si>
+    <t xml:space="preserve">Gjennomsnittlig gjeldsrente = rentekostnader × 100 / gjennomsnittlig gjeld. Krav: TKR &gt; gjennomsnittlig gjeldsrente (Økonomistyring 4.2.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Kapitalens omløpshastighet med to desimaler: salgsinntekt / gjennomsnittlig totalkapital. Svaret er et antall ganger, ikke en prosent.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kapitalens omløpshastighet = totale inntekter / gjennomsnittlig totalkapital (Økonomistyring 4.2.1). TKR = resultatgrad × omløpshastighet (kontrollen i avviksregisteret nr. 9).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Egenkapitalrentabiliteten er 47,9 %, mens totalkapitalrentabiliteten er 14,3 %. Hva er den viktigste grunnen til forskjellen?   A: Driften er bedre enn TKR viser, så EKR er det sanne tallet   B: Gjelden koster mindre enn kapitalen tjener, og gevinsten deles på en liten egenkapital   C: EKR regnes etter skatt, TKR før skatt   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Tom foreslår å låne 2 millioner kroner til, fordi «da blir egenkapitalrentabiliteten enda høyere». Hva svarer Kari? Skriv to setninger: én om risikoen, og én om hva hun heller vil gjøre med lønnsomheten.</t>
   </si>
   <si>
+    <t xml:space="preserve">Krav til TKR (Økonomistyring 4.2.1), egenkapitalandel og gjeldsgrad (4.2.4) og tiltakene for lønnsomhet i 4.2.1.1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gjennomsnittene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totalkapital: (9 400 000 + 10 182 650) / 2 = 9 791 325. Gjeld: (7 418 000 + 7 290 000) / 2. Sett parentes rundt hele gjennomsnittet på kalkulatoren.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvorfor 47,9 %?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sammenlikn TKR med gjeldsrenta. Hvem får differansen? Og hvor stor er egenkapitalen, nevneren i EKR, sammenliknet med totalkapitalen?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 4, avsnitt 4.2.1 (TKR, krav til TKR, gjennomsnittlig gjeldsrente, EKR og kapitalens omløpshastighet). Tallene er faktaarkets. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -179,18 +209,42 @@
     <t xml:space="preserve">a)  Resultatgraden i prosent med én desimal: (resultat før skatt + rentekostnader) × 100 / salgsinntekt.</t>
   </si>
   <si>
+    <t xml:space="preserve">Resultatgrad = (ordinært resultat før skatt + finanskostnader) × 100 / salgsinntekter (Økonomistyring 4.2.1). Krav ca. 10 % (tabell 4.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  TKR i prosent med én desimal: (resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital.</t>
   </si>
   <si>
+    <t xml:space="preserve">TKR = (ordinært resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital; krav TKR &gt; gjeldsrente og 8–10 % (Økonomistyring 4.2.1, tabell 4.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  EKR i prosent med én desimal: resultat før skatt × 100 / gjennomsnittlig egenkapital.</t>
   </si>
   <si>
+    <t xml:space="preserve">EKR = ordinært resultat før skatt × 100 / gjennomsnittlig egenkapital; krav 18–20 % (Økonomistyring 4.2.1, tabell 4.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Fjell kjøper materiell for 1 400 000 og selger det med 20 % påslag (avanse), altså for 1 680 000. Hvor mange prosent av materiellsalget er bruttofortjeneste?   A: 20 %   B: 16,7 %   C: 25 %   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Er Fjell Elektro lønnsom nok etter første år? Vurder resultatgraden, TKR og EKR mot kravene i boka, og foreslå ett tiltak på inntektssiden og ett på kostnadssiden.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kravene i tabell 4.2 og tiltakene i Økonomistyring 4.2.1.1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snitt fra start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fjell startet med 800 000 i totalkapital og 300 000 i egenkapital. Snitt = (start + 31.12.) / 2. Fjell har ingen renteinntekter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Påslaget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruttofortjenesten i kroner er 1 680 000 − 1 400 000. Del på salgsprisen, ikke på innkjøpet.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 4, avsnitt 4.2.1 med tiltakslisten i 4.2.1.1 og tabell 4.2. Resultatet er det samme som i OK09 (oppgave A2).</t>
   </si>
   <si>
@@ -236,18 +290,42 @@
     <t xml:space="preserve">a)  Likviditetsgrad 1 etter utbyttet, i prosent med én desimal: omløpsmidler × 100 / kortsiktig gjeld.</t>
   </si>
   <si>
+    <t xml:space="preserve">Likviditetsgrad 1 = omløpsmidler × 100 / kortsiktig gjeld; normtall 200 % (Økonomistyring 4.2.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Likviditetsgrad 2 etter utbyttet, i prosent med én desimal: (omløpsmidler − varelager) × 100 / kortsiktig gjeld.</t>
   </si>
   <si>
+    <t xml:space="preserve">Likviditetsgrad 2 = (omløpsmidler − varelager) × 100 / kortsiktig gjeld; normtall 100 % (Økonomistyring 4.2.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Egenkapitalandelen etter utbyttet, i prosent med én desimal: egenkapital × 100 / totalkapital (sum eiendeler).</t>
   </si>
   <si>
+    <t xml:space="preserve">Egenkapitalandel (soliditet) = egenkapital × 100 / totalkapital; gjeldsgrad = sum gjeld / egenkapital (Økonomistyring 4.2.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Tom sier: «Pengene finnes, vi hadde jo 910 650 kr i overskudd.» Hva er feil med resonnementet?   A: Ingenting: overskuddet står på bankkontoen og kan tas ut   B: Overskuddet er et resultat, ikke en beholdning: pengene står mest i kundefordringer og varelager   C: Overskuddet er feil regnet, fordi skatten ikke er trukket fra   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hva svarer Kari til Tom? Skriv to setninger: hva utbyttet gjør med betalingsevnen og soliditeten, og hva hun foreslår i stedet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Likviditet (4.2.2), arbeidskapital (4.2.3) og soliditet med tiltak (4.2.4 og 4.2.4.1) i Økonomistyring. Utbytte: aksjeloven § 3-4 og § 8-1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begge sider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utbyttet tar 600 000 fra bankinnskuddet (eiendelssiden) og fra egenkapitalen (finansieringssiden). Sum eiendeler blir 9 582 650. Den kortsiktige gjelden er den samme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Pengene finnes»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se på hvor omløpsmidlene står: 4 200 000 hos kundene, 1 400 000 på lageret, 982 650 på konto. Årsresultatet er ikke en bankkonto.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 4, avsnitt 4.2.2 (likviditetsgrad 1 og 2) og 4.2.4 (soliditet og tiltak). Utbytte: kap. 3.11 og aksjeloven § 3-4 og § 8-1 (Lovdata). Balansen er faktaarkets. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -281,12 +359,21 @@
     <t xml:space="preserve">a)  Likviditetsgrad 1 i prosent med én desimal: omløpsmidler × 100 / kortsiktig gjeld.</t>
   </si>
   <si>
+    <t xml:space="preserve">Likviditetsgrad 1 = omløpsmidler × 100 / kortsiktig gjeld; normtall 200 % (Økonomistyring 4.2.2), i dag ofte 100–200 % (Appendiks 1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Arbeidskapitalen i kroner: omløpsmidler − kortsiktig gjeld. Kontroller med egenkapital + langsiktig gjeld − anleggsmidler.</t>
   </si>
   <si>
+    <t xml:space="preserve">Arbeidskapital = omløpsmidler − kortsiktig gjeld = langsiktig kapital − anleggsmidler (Økonomistyring 4.2.3). Normer: minst halvparten av varelageret, eller 10–15 % av driftsinntektene.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Egenkapitalandelen i prosent med én desimal: egenkapital × 100 / totalkapital.</t>
   </si>
   <si>
+    <t xml:space="preserve">Egenkapitalandel = egenkapital × 100 / totalkapital; gjeldsgrad = sum gjeld / egenkapital, bør ikke overstige 5 (Økonomistyring 4.2.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hvilke av disse tiltakene bedrer egenkapitalandelen? Spør for hver: øker egenkapitalen, eller blir totalkapitalen mindre uten at egenkapitalen faller?</t>
   </si>
   <si>
@@ -309,6 +396,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Eieren vil kjøpe servicebilen for 400 000 kr på nytt banklån. Hva skjer med egenkapitalandelen og likviditetsgraden, og hva anbefaler du? To setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egenkapitalandel og gjeldsgrad (4.2.4), likviditetsgrad (4.2.2) og arbeidskapital (4.2.3) i Økonomistyring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeidskapitalen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omløpsmidler: lager + kunder + bank = 1 143 257. Trekk fra kortsiktig gjeld. Kontroll: egenkapital + banklån − utstyr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bil på lån</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilen øker anleggsmidlene og lånet øker langsiktig gjeld: begge med 400 000. Egenkapitalen står stille. Hva skjer med andelen?</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 4, avsnitt 4.2.2–4.2.4 med tiltakslisten i 4.2.4.1, og Appendiks 1 (normtall). Balansen 31.12. er ny for denne oppgaven.</t>
@@ -322,7 +424,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,8 +491,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -406,13 +530,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +607,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -542,11 +684,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -595,8 +757,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -610,7 +772,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -624,7 +786,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -927,7 +1089,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1088,35 +1250,20 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(3.2))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="B19" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(2.29))&lt;=0.01,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>41</v>
       </c>
@@ -1124,84 +1271,195 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
+      <c r="F21" s="17"/>
       <c r="G21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(3.2))&lt;=0.1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="18" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(2.29))&lt;=0.01,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>44</v>
+      </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="18" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1218,7 +1476,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1229,7 +1487,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1239,7 +1497,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1250,7 +1508,7 @@
     </row>
     <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1264,7 +1522,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>26</v>
@@ -1281,7 +1539,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="15" t="n">
@@ -1376,7 +1634,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1388,120 +1646,216 @@
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(13.2))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(ABS(F21-(31.2))&lt;=0.2,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="19"/>
+      <c r="F22" s="17"/>
       <c r="G22" s="18" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F22="","",IF(ABS(F22-(13.2))&lt;=0.1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18" t="str">
+        <f aca="false">IF(F25="","",IF(ABS(F25-(31.2))&lt;=0.2,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>65</v>
+      </c>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
       <c r="E26" s="20"/>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
     </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
+    <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="18" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="40" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:G26"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1518,7 +1872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1529,7 +1883,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1539,7 +1893,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1550,7 +1904,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1564,15 +1918,15 @@
         <v>24</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>3600000</v>
@@ -1583,7 +1937,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>1400000</v>
@@ -1594,7 +1948,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>4200000</v>
@@ -1605,7 +1959,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>982650</v>
@@ -1613,19 +1967,19 @@
       <c r="C11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="22" t="n">
+      <c r="A12" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="27" t="n">
         <v>6582650</v>
       </c>
       <c r="C12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="24" t="n">
+      <c r="A13" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="29" t="n">
         <v>10182650</v>
       </c>
       <c r="C13" s="17"/>
@@ -1641,7 +1995,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B15" s="15" t="n">
         <v>2800000</v>
@@ -1652,7 +2006,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>4490000</v>
@@ -1689,7 +2043,7 @@
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1701,120 +2055,216 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(ABS(F21-(102.1))&lt;=0.2,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="18" t="str">
-        <f aca="false">IF(F22="","",IF(ABS(F22-(23.9))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
+      <c r="F23" s="17"/>
       <c r="G23" s="18" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(ABS(F23-(102.1))&lt;=0.2,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="18" t="str">
+        <f aca="false">IF(F26="","",IF(ABS(F26-(23.9))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>92</v>
+      </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
       <c r="F27" s="20"/>
       <c r="G27" s="20"/>
     </row>
-    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
+    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="18" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:G27"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1831,7 +2281,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1842,7 +2292,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1852,7 +2302,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1863,7 +2313,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1874,15 +2324,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>240000</v>
@@ -1890,7 +2340,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>80000</v>
@@ -1898,7 +2348,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>500000</v>
@@ -1906,17 +2356,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>563257</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="22" t="n">
+      <c r="A12" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="27" t="n">
         <v>1383257</v>
       </c>
     </row>
@@ -1930,7 +2380,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>400000</v>
@@ -1938,17 +2388,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="B15" s="15" t="n">
         <v>600000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="22" t="n">
+      <c r="A16" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="27" t="n">
         <v>1383257</v>
       </c>
     </row>
@@ -1980,7 +2430,7 @@
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1992,205 +2442,301 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(ABS(F21-(543257))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="18" t="str">
-        <f aca="false">IF(F22="","",IF(ABS(F22-(27.7))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="18" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
+      <c r="F23" s="17"/>
+      <c r="G23" s="18" t="str">
+        <f aca="false">IF(F23="","",IF(ABS(F23-(543257))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="18" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+    </row>
+    <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="19"/>
+      <c r="F26" s="17"/>
       <c r="G26" s="18" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F26="","",IF(ABS(F26-(27.7))&lt;=0.1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="18" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="18" t="str">
-        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="18" t="str">
-        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-    </row>
-    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="18" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="18" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="18" t="str">
+        <f aca="false">IF(F32="","",IF(UPPER(TRIM(F32))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="18" t="str">
+        <f aca="false">IF(F33="","",IF(UPPER(TRIM(F33))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="18" t="str">
+        <f aca="false">IF(F34="","",IF(UPPER(TRIM(F34))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="18" t="str">
+        <f aca="false">IF(F35="","",IF(UPPER(TRIM(F35))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+    </row>
+    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+    </row>
+    <row r="47" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="25">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A31:G33"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A48:G48"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ok04/OK04_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok04/OK04_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Totalkapitalrentabiliteten (TKR) er det alle pengene i bedriften tjener: ordinært resultat før skatt pluss rentekostnader, delt på gjennomsnittlig totalkapital. Kravet i boka er at TKR er høyere enn den gjennomsnittlige gjeldsrenta, som er rentekostnader delt på gjennomsnittlig gjeld. Egenkapitalrentabiliteten (EKR) er resultat før skatt delt på gjennomsnittlig egenkapital. Når kapitalen tjener mer enn gjelden koster, går differansen til eierne, og er egenkapitalen liten, blir EKR stor. Kapitalens omløpshastighet er salgsinntekt delt på gjennomsnittlig totalkapital.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til regnskapsåret 2026; regnestykket er det samme uansett når du gjør det. Kari Nordlund og Tom Berg eier Nordlys Elektro AS. Regnskapsføreren har regnet ut at de fikk 47,9 % avkastning på egenkapitalen før skatt. Tom vil låne mer for å få tallet enda høyere. Kari vil først vite hva det er som gir de 47,9 prosentene. Tallene fra resultatregnskapet og balansen står i tabellen. Gå fram slik: regn gjennomsnittene først ((1. januar + 31. desember) / 2), så TKR, så gjennomsnittlig gjeldsrente, så kapitalens omløpshastighet. Sammenlikn TKR med gjeldsrenta.</t>
+    <t xml:space="preserve">Casen er lagt til regnskapsåret 2026; regnestykket er det samme uansett når du gjør det. Kari Nordlund og Tom Berg eier Nordlys Elektro AS. Regnskapsføreren har regnet ut at de fikk 47,9 % avkastning på egenkapitalen før skatt. Tom vil låne mer for å få tallet enda høyere. Kari vil først vite hva det er som gir de 47,9 prosentene. Tallene fra resultatregnskapet og balansen står i tabellen. Gå fram slik: regn gjennomsnittene først ((1. januar + 31. desember) / 2), så totalkapitalrentabilitet (TKR), så gjennomsnittlig gjeldsrente, så kapitalens omløpshastighet. Sammenlikn TKR med gjeldsrenta.</t>
   </si>
   <si>
     <t xml:space="preserve">Kr</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">Formel og begrep</t>
   </si>
   <si>
-    <t xml:space="preserve">TKR = (ordinært resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital (Økonomistyring 4.2.1). Gjennomsnitt = (IB + UB) / 2.</t>
+    <t xml:space="preserve">Totalkapitalrentabilitet = (ordinært resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital (Økonomistyring 4.2.1). Gjennomsnitt = (verdi 1.1. + verdi 31.12.) / 2.</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Gjennomsnittlig gjeldsrente i prosent med én desimal: rentekostnader × 100 / gjennomsnittlig gjeld.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gjennomsnittlig gjeldsrente = rentekostnader × 100 / gjennomsnittlig gjeld. Krav: TKR &gt; gjennomsnittlig gjeldsrente (Økonomistyring 4.2.1).</t>
+    <t xml:space="preserve">Gjennomsnittlig gjeldsrente = rentekostnader × 100 / gjennomsnittlig gjeld. Krav: totalkapitalrentabilitet &gt; gjennomsnittlig gjeldsrente (Økonomistyring 4.2.1).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Kapitalens omløpshastighet med to desimaler: salgsinntekt / gjennomsnittlig totalkapital. Svaret er et antall ganger, ikke en prosent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kapitalens omløpshastighet = totale inntekter / gjennomsnittlig totalkapital (Økonomistyring 4.2.1). TKR = resultatgrad × omløpshastighet (kontrollen i avviksregisteret nr. 9).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d)  Egenkapitalrentabiliteten er 47,9 %, mens totalkapitalrentabiliteten er 14,3 %. Hva er den viktigste grunnen til forskjellen?   A: Driften er bedre enn TKR viser, så EKR er det sanne tallet   B: Gjelden koster mindre enn kapitalen tjener, og gevinsten deles på en liten egenkapital   C: EKR regnes etter skatt, TKR før skatt   (skriv bokstaven)</t>
+    <t xml:space="preserve">Kapitalens omløpshastighet = totale inntekter / gjennomsnittlig totalkapital (Økonomistyring 4.2.1). Totalkapitalrentabilitet = resultatgrad × omløpshastighet (kontrollen i avviksregisteret nr. 9).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d)  Egenkapitalrentabiliteten er 47,9 %, mens totalkapitalrentabiliteten er 14,3 %. Hva er den viktigste grunnen til forskjellen?   A: Driften er bedre enn totalkapitalrentabilitet viser, så egenkapitalrentabilitet er det sanne tallet   B: Gjelden koster mindre enn kapitalen tjener, og gevinsten deles på en liten egenkapital   C: Egenkapitalrentabilitet regnes etter skatt, totalkapitalrentabilitet før skatt   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Tom foreslår å låne 2 millioner kroner til, fordi «da blir egenkapitalrentabiliteten enda høyere». Hva svarer Kari? Skriv to setninger: én om risikoen, og én om hva hun heller vil gjøre med lønnsomheten.</t>
   </si>
   <si>
-    <t xml:space="preserve">Krav til TKR (Økonomistyring 4.2.1), egenkapitalandel og gjeldsgrad (4.2.4) og tiltakene for lønnsomhet i 4.2.1.1.</t>
+    <t xml:space="preserve">Krav til totalkapitalrentabilitet (Økonomistyring 4.2.1), egenkapitalandel og gjeldsgrad (4.2.4) og tiltakene for lønnsomhet i 4.2.1.1.</t>
   </si>
   <si>
     <t xml:space="preserve">Hint, hvis du står fast</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">Hvorfor 47,9 %?</t>
   </si>
   <si>
-    <t xml:space="preserve">Sammenlikn TKR med gjeldsrenta. Hvem får differansen? Og hvor stor er egenkapitalen, nevneren i EKR, sammenliknet med totalkapitalen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 4, avsnitt 4.2.1 (TKR, krav til TKR, gjennomsnittlig gjeldsrente, EKR og kapitalens omløpshastighet). Tallene er faktaarkets. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Sammenlikn totalkapitalrentabilitet med gjeldsrenta. Hvem får differansen? Og hvor stor er egenkapitalen, nevneren i egenkapitalrentabilitet, sammenliknet med totalkapitalen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 4, avsnitt 4.2.1 (totalkapitalrentabilitet og kravet til den, gjennomsnittlig gjeldsrente, egenkapitalrentabilitet og kapitalens omløpshastighet). Tallene er faktaarkets. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">Regnearket er øvingsstøtte. Det kan ikke siteres eller vises til i besvarelser, prosjektoppgaver eller eksamen; der gjelder læreboka og oppgitte primærkilder.</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">A2 · Fjell Elektro etter første driftsår: er bedriften lønnsom nok?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Resultatgraden er resultat før skatt pluss rentekostnader, i prosent av salgsinntekten. TKR er det samme beløpet delt på gjennomsnittlig totalkapital, og EKR er resultat før skatt delt på gjennomsnittlig egenkapital. Gjennomsnitt er (start + slutt) / 2. Boka sier ca. 10 % for resultatgrad og driftsmargin, 8–10 % for TKR og 18–20 % for EKR, men kravene varierer mellom bransjer. Bruttofortjeneste regnes av salgsprisen, avanse av innkjøpsprisen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i kapittel 9) har drevet i ett år, og regnskapet er ferdig. Banken vil vite om bedriften er lønnsom nok før den sier ja til en kassekreditt. Bedriften startet med aksjekapital 300 000 og banklån 500 000, altså 800 000 i totalkapital. Ved årets slutt er totalkapitalen 1 383 257. Bruk tallene i tabellen. Regn gjennomsnittene først, så resultatgrad, TKR og EKR, og sammenlikn med kravene i boka.</t>
+    <t xml:space="preserve">Kort oppsummert: Resultatgraden er resultat før skatt pluss rentekostnader, i prosent av salgsinntekten. Totalkapitalrentabilitet (TKR) er det samme beløpet delt på gjennomsnittlig totalkapital, og egenkapitalrentabilitet (EKR) er resultat før skatt delt på gjennomsnittlig egenkapital. Gjennomsnitt er (start + slutt) / 2. Boka sier cirka 10 % for resultatgrad og driftsmargin, 8–10 % for TKR og 18–20 % for EKR, men kravene varierer mellom bransjer. Bruttofortjeneste regnes av salgsprisen, avanse av innkjøpsprisen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i kapittel 9) har drevet i ett år, og regnskapet er ferdig. Banken vil vite om bedriften er lønnsom nok før den sier ja til en kassekreditt. Bedriften startet med aksjekapital 300 000 og banklån 500 000, altså 800 000 i totalkapital. Ved årets slutt er totalkapitalen 1 383 257. Bruk tallene i tabellen. Regn gjennomsnittene først, så resultatgrad, totalkapitalrentabilitet og egenkapitalrentabilitet, og sammenlikn med kravene i boka.</t>
   </si>
   <si>
     <t xml:space="preserve">Ved start</t>
@@ -209,25 +209,25 @@
     <t xml:space="preserve">a)  Resultatgraden i prosent med én desimal: (resultat før skatt + rentekostnader) × 100 / salgsinntekt.</t>
   </si>
   <si>
-    <t xml:space="preserve">Resultatgrad = (ordinært resultat før skatt + finanskostnader) × 100 / salgsinntekter (Økonomistyring 4.2.1). Krav ca. 10 % (tabell 4.2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b)  TKR i prosent med én desimal: (resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TKR = (ordinært resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital; krav TKR &gt; gjeldsrente og 8–10 % (Økonomistyring 4.2.1, tabell 4.2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)  EKR i prosent med én desimal: resultat før skatt × 100 / gjennomsnittlig egenkapital.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EKR = ordinært resultat før skatt × 100 / gjennomsnittlig egenkapital; krav 18–20 % (Økonomistyring 4.2.1, tabell 4.2).</t>
+    <t xml:space="preserve">Resultatgrad = (ordinært resultat før skatt + finanskostnader) × 100 / salgsinntekter (Økonomistyring 4.2.1). Krav cirka 10 % (tabell 4.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b)  Totalkapitalrentabilitet i prosent med én desimal: (resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totalkapitalrentabilitet = (ordinært resultat før skatt + rentekostnader) × 100 / gjennomsnittlig totalkapital; krav totalkapitalrentabilitet &gt; gjeldsrente og 8–10 % (Økonomistyring 4.2.1, tabell 4.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)  Egenkapitalrentabilitet i prosent med én desimal: resultat før skatt × 100 / gjennomsnittlig egenkapital.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egenkapitalrentabilitet = ordinært resultat før skatt × 100 / gjennomsnittlig egenkapital; krav 18–20 % (Økonomistyring 4.2.1, tabell 4.2).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Fjell kjøper materiell for 1 400 000 og selger det med 20 % påslag (avanse), altså for 1 680 000. Hvor mange prosent av materiellsalget er bruttofortjeneste?   A: 20 %   B: 16,7 %   C: 25 %   (skriv bokstaven)</t>
   </si>
   <si>
-    <t xml:space="preserve">e)  Er Fjell Elektro lønnsom nok etter første år? Vurder resultatgraden, TKR og EKR mot kravene i boka, og foreslå ett tiltak på inntektssiden og ett på kostnadssiden.</t>
+    <t xml:space="preserve">e)  Er Fjell Elektro lønnsom nok etter første år? Vurder resultatgraden, totalkapitalrentabilitet og egenkapitalrentabilitet mot kravene i boka, og foreslå ett tiltak på inntektssiden og ett på kostnadssiden.</t>
   </si>
   <si>
     <t xml:space="preserve">Kravene i tabell 4.2 og tiltakene i Økonomistyring 4.2.1.1.</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">Bruttofortjenesten i kroner er 1 680 000 − 1 400 000. Del på salgsprisen, ikke på innkjøpet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 4, avsnitt 4.2.1 med tiltakslisten i 4.2.1.1 og tabell 4.2. Resultatet er det samme som i OK09 (oppgave A2).</t>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 4, avsnitt 4.2.1 med tiltakslisten i 4.2.1.1 og tabell 4.2. Resultatet er det samme som i kapittel 9 (oppgave A2).</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: tåler bedriften 600 000 kr i utbytte?</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">Kort oppsummert: Likviditetsgrad 1 = omløpsmidler × 100 / kortsiktig gjeld (normtall 200 %, i dag aksepteres 100–200 %). Arbeidskapital = omløpsmidler − kortsiktig gjeld, og den må være positiv. Egenkapitalandel = egenkapital × 100 / totalkapital (35 % eller mer er godt). Egenkapitalandelen bedres bare ved å la overskudd stå, betale ned gjeld eller skyte inn ny egenkapital.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS har drevet i ett år. Eieren vil kjøpe en tredje servicebil for 400 000 kr og finansiere den med et nytt banklån, og banken ber om en vurdering av betalingsevne, finansiering og soliditet først. Balansen 31.12. står i tabellen. Kundefordringene er desembersalget med mva (30 dagers kredittid), og varelageret er materiell kjøpt inn til januarjobbene. Den kortsiktige gjelden på 600 000 er leverandørgjeld 100 000, skyldig mva, skattetrekk og arbeidsgiveravgift 258 117, skyldige feriepenger 218 400 og betalbar skatt 23 483. Regn nøkkeltallene i dag, og vurder hva bilen på lån gjør med dem.</t>
+    <t xml:space="preserve">Fjell Elektro AS har drevet i ett år. Eieren vil kjøpe en tredje servicebil for 400 000 kr og finansiere den med et nytt banklån, og banken ber om en vurdering av betalingsevne, finansiering og soliditet først. Balansen 31.12. står i tabellen. Kundefordringene er desembersalget med merverdiavgift (30 dagers kredittid), og varelageret er materiell kjøpt inn til januarjobbene. Den kortsiktige gjelden på 600 000 er leverandørgjeld 100 000, skyldig merverdiavgift, skattetrekk og arbeidsgiveravgift 258 117, skyldige feriepenger 218 400 og betalbar skatt 23 483. Regn nøkkeltallene i dag, og vurder hva bilen på lån gjør med dem.</t>
   </si>
   <si>
     <t xml:space="preserve">Balanse 31.12. (kr)</t>
@@ -1304,7 +1304,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
         <v>39</v>
       </c>
@@ -1317,7 +1317,7 @@
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
         <v>45</v>
       </c>
@@ -1506,7 +1506,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>57</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
         <v>39</v>
       </c>
@@ -1686,7 +1686,7 @@
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
     </row>
-    <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
         <v>64</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
         <v>67</v>
       </c>

--- a/pensum/ok04/OK04_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok04/OK04_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="130">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 4: Regnskapsanalyse (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 4: Regnskapsanalyse (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ok04/OK04_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok04/OK04_Klasseoppgaver_v5.xlsx
@@ -161,7 +161,7 @@
     <t xml:space="preserve">Kapitalens omløpshastighet = totale inntekter / gjennomsnittlig totalkapital (Økonomistyring 4.2.1). Totalkapitalrentabilitet = resultatgrad × omløpshastighet (kontrollen i avviksregisteret nr. 9).</t>
   </si>
   <si>
-    <t xml:space="preserve">d)  Egenkapitalrentabiliteten er 47,9 %, mens totalkapitalrentabiliteten er 14,3 %. Hva er den viktigste grunnen til forskjellen?   A: Driften er bedre enn totalkapitalrentabilitet viser, så egenkapitalrentabilitet er det sanne tallet   B: Gjelden koster mindre enn kapitalen tjener, og gevinsten deles på en liten egenkapital   C: Egenkapitalrentabilitet regnes etter skatt, totalkapitalrentabilitet før skatt   (skriv bokstaven)</t>
+    <t xml:space="preserve">d)  Egenkapitalrentabiliteten er 47,9 % (1 167 500 / snittegenkapital 2 437 325), mens totalkapitalrentabiliteten er 14,3 % (det du fant i a). Hva er den viktigste grunnen til forskjellen?   A: Driften er bedre enn totalkapitalrentabilitet viser, så egenkapitalrentabilitet er det sanne tallet   B: Gjelden koster mindre enn kapitalen tjener, og gevinsten deles på en liten egenkapital   C: Egenkapitalrentabilitet regnes etter skatt, totalkapitalrentabilitet før skatt   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Tom foreslår å låne 2 millioner kroner til, fordi «da blir egenkapitalrentabiliteten enda høyere». Hva svarer Kari? Skriv to setninger: én om risikoen, og én om hva hun heller vil gjøre med lønnsomheten.</t>
@@ -1317,7 +1317,7 @@
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="27" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
         <v>45</v>
       </c>
